--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_常量表_Combat_CombatConstantConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="537">
   <si>
     <t>常量键</t>
   </si>
@@ -1628,6 +1628,21 @@
   </si>
   <si>
     <t>StepB 飞入中 Image 白↔红闪烁 Hz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ParabolaForwardArcDegrees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">抛物线前方张角</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full forward arc degrees for Parabola block and melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">抛物线挡射与近战扇形全角</t>
   </si>
 </sst>
 </file>
@@ -2605,7 +2620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7272727272727" customWidth="1"/>
@@ -4824,6 +4839,23 @@
         <v>531</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>532</v>
+      </c>
+      <c r="B131" t="s">
+        <v>533</v>
+      </c>
+      <c r="C131" t="s">
+        <v>534</v>
+      </c>
+      <c r="D131" t="s">
+        <v>535</v>
+      </c>
+      <c r="E131" t="s">
+        <v>536</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
